--- a/equipment_tracking_forms/024_hardware_usage_monitoring_checklist_form--equipment_tracking_forms.xlsx
+++ b/equipment_tracking_forms/024_hardware_usage_monitoring_checklist_form--equipment_tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -830,8 +830,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -859,12 +859,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'user_1',_'value':_'user_1'}</t>
+          <t>user_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'User 1', 'value': 'User 1'}</t>
+          <t>User 1</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'user_2',_'value':_'user_2'}</t>
+          <t>user_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'User 2', 'value': 'User 2'}</t>
+          <t>User 2</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'user_3',_'value':_'user_3'}</t>
+          <t>user_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'User 3', 'value': 'User 3'}</t>
+          <t>User 3</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'equipment_a',_'value':_'equipment_a'}</t>
+          <t>equipment_a</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Equipment A', 'value': 'Equipment A'}</t>
+          <t>Equipment A</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'equipment_b',_'value':_'equipment_b'}</t>
+          <t>equipment_b</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Equipment B', 'value': 'Equipment B'}</t>
+          <t>Equipment B</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'active',_'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Active', 'value': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'inactive',_'value':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Inactive', 'value': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'damage',_'value':_'damage'}</t>
+          <t>damage</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Damage', 'value': 'Damage'}</t>
+          <t>Damage</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'wear_and_tear',_'value':_'wear_and_tear'}</t>
+          <t>wear_and_tear</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Wear and tear', 'value': 'Wear and tear'}</t>
+          <t>Wear and tear</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'none_of_the_above',_'value':_'none_of_the_above'}</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'None of the above', 'value': 'None of the above'}</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'broken',_'value':_'broken'}</t>
+          <t>broken</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Broken', 'value': 'Broken'}</t>
+          <t>Broken</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'not_broken',_'value':_'not_broken'}</t>
+          <t>not_broken</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Not broken', 'value': 'Not broken'}</t>
+          <t>Not broken</t>
         </is>
       </c>
     </row>
